--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-28T11:06:38.643Z</t>
+    <t>2026-04-28T11:53:35.840Z</t>
   </si>
   <si>
     <t>Stryker - Medical Devices and Equipment Manufacturing Company | Stryker</t>
@@ -73,7 +73,7 @@
     <t>hub-page</t>
   </si>
   <si>
-    <t>2026-04-28T09:58:27.456Z</t>
+    <t>2026-04-28T11:53:31.377Z</t>
   </si>
   <si>
     <t>Training and education | Stryker</t>
@@ -94,7 +94,7 @@
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-04-28T09:29:20.137Z</t>
+    <t>2026-04-28T11:53:27.329Z</t>
   </si>
   <si>
     <t>RISE | Stryker</t>
@@ -115,7 +115,7 @@
     <t>training-article</t>
   </si>
   <si>
-    <t>2026-04-24T08:09:47.636Z</t>
+    <t>2026-04-28T11:51:20.661Z</t>
   </si>
   <si>
     <t>Cardiovascular health | Stryker</t>
@@ -133,7 +133,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/caregiver-safety</t>
   </si>
   <si>
-    <t>2026-04-24T08:09:54.150Z</t>
+    <t>2026-04-28T11:51:27.992Z</t>
   </si>
   <si>
     <t>Caregiver safety | Stryker</t>
@@ -151,7 +151,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/cerebrovascular-health</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:00.666Z</t>
+    <t>2026-04-28T11:51:32.870Z</t>
   </si>
   <si>
     <t>Cerebrovascular health | Stryker</t>
@@ -166,7 +166,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/complex-surgical-access-and-decompression</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:06.477Z</t>
+    <t>2026-04-28T11:51:37.409Z</t>
   </si>
   <si>
     <t>Complex surgical access and decompression | Stryker</t>
@@ -181,7 +181,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/cranial-procedures-and-repair</t>
   </si>
   <si>
-    <t>2026-04-24T08:06:45.172Z</t>
+    <t>2026-04-28T11:52:37.368Z</t>
   </si>
   <si>
     <t>Cranial procedures and repair | Stryker</t>
@@ -199,7 +199,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/fall-prevention</t>
   </si>
   <si>
-    <t>2026-04-24T08:06:40.590Z</t>
+    <t>2026-04-28T11:52:31.980Z</t>
   </si>
   <si>
     <t>Fall prevention | Stryker</t>
@@ -217,7 +217,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/healthcare-teamwork-and-communication</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:12.773Z</t>
+    <t>2026-04-28T11:51:41.716Z</t>
   </si>
   <si>
     <t>Healthcare teamwork and communication | Stryker</t>
@@ -235,7 +235,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/hospital-acquired-infections</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:18.427Z</t>
+    <t>2026-04-28T11:51:49.602Z</t>
   </si>
   <si>
     <t>Hospital-acquired infections | Stryker</t>
@@ -253,7 +253,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/mobility</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:22.735Z</t>
+    <t>2026-04-28T11:51:56.544Z</t>
   </si>
   <si>
     <t>Mobility | Stryker</t>
@@ -271,7 +271,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/pressure-injuries</t>
   </si>
   <si>
-    <t>2026-04-24T07:52:34.920Z</t>
+    <t>2026-04-28T11:51:16.410Z</t>
   </si>
   <si>
     <t>Pressure injuries | Stryker</t>
@@ -289,7 +289,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/surgical-access-and-visualization</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:27.863Z</t>
+    <t>2026-04-28T11:52:02.706Z</t>
   </si>
   <si>
     <t>Surgical access and visualization | Stryker</t>
@@ -307,7 +307,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/upcoming-events</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:39.836Z</t>
+    <t>2026-04-28T11:52:13.855Z</t>
   </si>
   <si>
     <t>FocusRN upcoming events | Stryker</t>
@@ -325,7 +325,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/waste-management-practices</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:47.019Z</t>
+    <t>2026-04-28T11:52:21.602Z</t>
   </si>
   <si>
     <t>Waste management practices | Stryker</t>
@@ -340,7 +340,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/womens-health</t>
   </si>
   <si>
-    <t>2026-04-24T08:10:53.126Z</t>
+    <t>2026-04-28T11:52:26.978Z</t>
   </si>
   <si>
     <t>Women's health | Stryker</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-28T11:53:35.840Z</t>
+    <t>2026-04-28T12:07:48.143Z</t>
   </si>
   <si>
     <t>Stryker - Medical Devices and Equipment Manufacturing Company | Stryker</t>
@@ -73,7 +73,7 @@
     <t>hub-page</t>
   </si>
   <si>
-    <t>2026-04-28T11:53:31.377Z</t>
+    <t>2026-04-28T12:07:44.000Z</t>
   </si>
   <si>
     <t>Training and education | Stryker</t>
@@ -94,7 +94,7 @@
     <t>product-page</t>
   </si>
   <si>
-    <t>2026-04-28T11:53:27.329Z</t>
+    <t>2026-04-28T12:07:39.104Z</t>
   </si>
   <si>
     <t>RISE | Stryker</t>
@@ -115,7 +115,7 @@
     <t>training-article</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:20.661Z</t>
+    <t>2026-04-28T12:06:03.051Z</t>
   </si>
   <si>
     <t>Cardiovascular health | Stryker</t>
@@ -133,7 +133,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/caregiver-safety</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:27.992Z</t>
+    <t>2026-04-28T12:06:09.357Z</t>
   </si>
   <si>
     <t>Caregiver safety | Stryker</t>
@@ -151,7 +151,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/cerebrovascular-health</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:32.870Z</t>
+    <t>2026-04-28T12:06:15.175Z</t>
   </si>
   <si>
     <t>Cerebrovascular health | Stryker</t>
@@ -166,7 +166,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/complex-surgical-access-and-decompression</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:37.409Z</t>
+    <t>2026-04-28T12:06:21.354Z</t>
   </si>
   <si>
     <t>Complex surgical access and decompression | Stryker</t>
@@ -181,7 +181,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/cranial-procedures-and-repair</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:37.368Z</t>
+    <t>2026-04-28T12:07:17.709Z</t>
   </si>
   <si>
     <t>Cranial procedures and repair | Stryker</t>
@@ -199,7 +199,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/fall-prevention</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:31.980Z</t>
+    <t>2026-04-28T12:07:13.282Z</t>
   </si>
   <si>
     <t>Fall prevention | Stryker</t>
@@ -217,7 +217,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/healthcare-teamwork-and-communication</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:41.716Z</t>
+    <t>2026-04-28T12:06:25.625Z</t>
   </si>
   <si>
     <t>Healthcare teamwork and communication | Stryker</t>
@@ -235,7 +235,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/hospital-acquired-infections</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:49.602Z</t>
+    <t>2026-04-28T12:06:31.050Z</t>
   </si>
   <si>
     <t>Hospital-acquired infections | Stryker</t>
@@ -253,7 +253,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/mobility</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:56.544Z</t>
+    <t>2026-04-28T12:06:35.678Z</t>
   </si>
   <si>
     <t>Mobility | Stryker</t>
@@ -271,7 +271,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/pressure-injuries</t>
   </si>
   <si>
-    <t>2026-04-28T11:51:16.410Z</t>
+    <t>2026-04-28T12:05:59.115Z</t>
   </si>
   <si>
     <t>Pressure injuries | Stryker</t>
@@ -289,7 +289,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/surgical-access-and-visualization</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:02.706Z</t>
+    <t>2026-04-28T12:06:40.023Z</t>
   </si>
   <si>
     <t>Surgical access and visualization | Stryker</t>
@@ -307,7 +307,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/upcoming-events</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:13.855Z</t>
+    <t>2026-04-28T12:06:59.663Z</t>
   </si>
   <si>
     <t>FocusRN upcoming events | Stryker</t>
@@ -325,7 +325,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/waste-management-practices</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:21.602Z</t>
+    <t>2026-04-28T12:07:04.828Z</t>
   </si>
   <si>
     <t>Waste management practices | Stryker</t>
@@ -340,7 +340,7 @@
     <t>us/en/training-and-education/medical-and-surgical-equipment/sage/focusrn/womens-health</t>
   </si>
   <si>
-    <t>2026-04-28T11:52:26.978Z</t>
+    <t>2026-04-28T12:07:09.336Z</t>
   </si>
   <si>
     <t>Women's health | Stryker</t>
